--- a/naver-place-crawler/results_nail/청주_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/청주_네일샵.xlsx
@@ -421,18 +421,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,34 +564,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>티아나뷰티</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>tiananail@naver.com</t>
-        </is>
-      </c>
+          <t>프롬네일 청주율량점</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1447-2590</t>
+          <t>0507-1336-8451</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>충북 청주시 청원구 향군로59번길 9 1층 티아나뷰티</t>
+          <t>충북 청주시 청원구 율량로 152</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://link.thinkofyou.kr/tianabeauty</t>
+          <t>https://www.instagram.com/fromnail__</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -606,17 +602,13 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4249t</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1166</v>
+        <v>928</v>
       </c>
       <c r="Q2" t="n">
-        <v>212</v>
+        <v>61</v>
       </c>
       <c r="R2" t="n">
-        <v>1378</v>
+        <v>989</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +632,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1861241419</t>
+          <t>1014461310</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1861241419</t>
+          <t>https://m.place.naver.com/place/1014461310</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -662,39 +654,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>벨르뮤 네일&amp;아카데미</t>
+          <t>티아나뷰티</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ye__r2@naver.com</t>
+          <t>tiananail@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1456-3478</t>
+          <t>0507-1447-2590</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 서현동로 17 4층 403호</t>
+          <t>충북 청주시 청원구 향군로59번길 9 1층 티아나뷰티</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://link.thinkofyou.kr/tianabeauty</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -709,27 +701,27 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5y755</t>
+          <t>https://talk.naver.com/ct/w4249t</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>784</v>
+        <v>1173</v>
       </c>
       <c r="Q3" t="n">
-        <v>363</v>
+        <v>226</v>
       </c>
       <c r="R3" t="n">
-        <v>1147</v>
+        <v>1399</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1574225057</t>
+          <t>1861241419</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1574225057</t>
+          <t>https://m.place.naver.com/place/1861241419</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -760,29 +752,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>네일드메종</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>doalog13@naver.com</t>
-        </is>
-      </c>
+          <t>수에브</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1375-3528</t>
+          <t>0507-1402-1489</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 서현로 68 상가동 B105호 (뚜레쥬르 옆)</t>
+          <t>충북 청주시 흥덕구 2순환로1219번길 30 힐스에비뉴 청주센트럴 상가2층 234호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_de_maison</t>
+          <t>https://www.instagram.com/_sueve_</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,12 +795,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5x0t1</t>
+          <t>https://talk.naver.com/ct/w980geq</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>403</v>
+        <v>563</v>
       </c>
       <c r="Q4" t="n">
-        <v>164</v>
+        <v>31</v>
       </c>
       <c r="R4" t="n">
-        <v>567</v>
+        <v>594</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1226084837</t>
+          <t>2071380519</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1226084837</t>
+          <t>https://m.place.naver.com/place/2071380519</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -858,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>시에뷰티네일 청주오창점</t>
+          <t>르엔느뷰티</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ses3441@naver.com</t>
+          <t>seolhee10@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1371-2507</t>
+          <t>0507-1450-9981</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>충북 청주시 청원구 오창읍 중심상업로 14 대운프라자 9층 902호</t>
+          <t>충북 청주시 상당구 상당로143번길 41 1층 르엔느뷰티</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ses3441</t>
+          <t>http://www.instagram.com/leannebeauty__</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,7 +893,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5itbc</t>
+          <t>https://talk.naver.com/ct/wcfe7o</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>590</v>
+        <v>1540</v>
       </c>
       <c r="Q5" t="n">
-        <v>1814</v>
+        <v>67</v>
       </c>
       <c r="R5" t="n">
-        <v>2404</v>
+        <v>1607</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +922,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1916898751</t>
+          <t>38426934</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1916898751</t>
+          <t>https://m.place.naver.com/place/38426934</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -956,29 +944,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>네일윰</t>
+          <t>네일드메종</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6643yumi@naver.com</t>
+          <t>doalog13@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1418-1885</t>
+          <t>0507-1375-3528</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>충북 청주시 상당구 용암북로4번길 78 1층</t>
+          <t>충북 청주시 흥덕구 서현로 68 상가동 B105호 (뚜레쥬르 옆)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/6643yumi</t>
+          <t>https://www.instagram.com/nail_de_maison</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,7 +981,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +991,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4r7w1</t>
+          <t>https://talk.naver.com/ct/w5x0t1</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1005,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>139</v>
+        <v>404</v>
       </c>
       <c r="Q6" t="n">
-        <v>202</v>
+        <v>164</v>
       </c>
       <c r="R6" t="n">
-        <v>341</v>
+        <v>568</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1020,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1169028429</t>
+          <t>1226084837</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1169028429</t>
+          <t>https://m.place.naver.com/place/1226084837</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1057,11 +1045,7 @@
           <t>감각네일 용암점</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ssh0206ody@naver.com</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
@@ -1115,13 +1099,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="Q7" t="n">
         <v>1375</v>
       </c>
       <c r="R7" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1140,7 +1124,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1136,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>제이원뷰티</t>
+          <t>복대동 네일코코</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kkkong44@naver.com</t>
+          <t>ejkim0422@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1392-5576</t>
+          <t>0507-1371-4016</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충북 청주시 청원구 주성로 293 102호 제이원뷰티</t>
+          <t>충북 청주시 흥덕구 증안로34번길 28-13 1층 네일코코</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/j.won_beauty_</t>
+          <t>https://www.instagram.com/nailcoco_j</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1199,7 +1183,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5wqlj</t>
+          <t>https://talk.naver.com/ct/w443mv</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1197,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="Q8" t="n">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="R8" t="n">
-        <v>254</v>
+        <v>173</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1212,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1062324570</t>
+          <t>1130129691</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1062324570</t>
+          <t>https://m.place.naver.com/place/1130129691</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1234,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>복대동 네일코코</t>
+          <t>엔브뷰티</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>appie8003@naver.com</t>
+          <t>dmsql8424@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1371-4016</t>
+          <t>0507-1331-4116</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 증안로34번길 28-13 1층 네일코코</t>
+          <t>충북 청주시 상당구 용담로 7 쁘띠칸타빌 137호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailcoco_j</t>
+          <t>https://http//pf.kakao.com/_Mbxclxb</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1292,17 +1276,13 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w443mv</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1311,13 +1291,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="Q9" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="R9" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,17 +1306,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1130129691</t>
+          <t>1110185687</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1130129691</t>
+          <t>https://m.place.naver.com/place/1110185687</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1348,25 +1328,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>엔브뷰티</t>
+          <t>네일은봄날</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dmsql8424@naver.com</t>
+          <t>bomnal6878@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1401-6878</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충북 청주시 상당구 용담로 7 쁘띠칸타빌 137호</t>
+          <t>충북 청주시 흥덕구 2순환로 1106 서청주파크자이 상가동 120호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://http//pf.kakao.com/_Mbxclxb</t>
+          <t>https://www.instagram.com/bomnal_official_</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1386,13 +1370,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wek5mvd</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1401,13 +1389,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>151</v>
+        <v>37</v>
       </c>
       <c r="Q10" t="n">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="R10" t="n">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,17 +1404,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1110185687</t>
+          <t>37892074</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1110185687</t>
+          <t>https://m.place.naver.com/place/37892074</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1499,13 +1487,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="Q11" t="n">
         <v>41</v>
       </c>
       <c r="R11" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1524,7 +1512,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/청주_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/청주_네일샵.xlsx
@@ -422,12 +422,12 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="48" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -567,7 +567,11 @@
           <t>프롬네일 청주율량점</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>jsyong25@naver.com</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
@@ -617,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="Q2" t="n">
         <v>61</v>
       </c>
       <c r="R2" t="n">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -642,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -654,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>티아나뷰티</t>
+          <t>르엔느뷰티</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>tiananail@naver.com</t>
+          <t>seolhee10@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1447-2590</t>
+          <t>0507-1450-9981</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>충북 청주시 청원구 향군로59번길 9 1층 티아나뷰티</t>
+          <t>충북 청주시 상당구 상당로143번길 41 1층 르엔느뷰티</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://link.thinkofyou.kr/tianabeauty</t>
+          <t>http://www.instagram.com/leannebeauty__</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -701,12 +705,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4249t</t>
+          <t>https://talk.naver.com/ct/wcfe7o</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1173</v>
+        <v>1545</v>
       </c>
       <c r="Q3" t="n">
-        <v>226</v>
+        <v>67</v>
       </c>
       <c r="R3" t="n">
-        <v>1399</v>
+        <v>1612</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1861241419</t>
+          <t>38426934</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1861241419</t>
+          <t>https://m.place.naver.com/place/38426934</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -752,30 +756,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>수에브</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>티아나뷰티</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>tiananail@naver.com</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1402-1489</t>
+          <t>0507-1447-2590</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 2순환로1219번길 30 힐스에비뉴 청주센트럴 상가2층 234호</t>
+          <t>충북 청주시 청원구 향군로59번길 9 1층 티아나뷰티</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_sueve_</t>
+          <t>https://link.thinkofyou.kr/tianabeauty</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -795,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w980geq</t>
+          <t>https://talk.naver.com/ct/w4249t</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -809,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>563</v>
+        <v>1179</v>
       </c>
       <c r="Q4" t="n">
-        <v>31</v>
+        <v>226</v>
       </c>
       <c r="R4" t="n">
-        <v>594</v>
+        <v>1405</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2071380519</t>
+          <t>1861241419</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2071380519</t>
+          <t>https://m.place.naver.com/place/1861241419</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -846,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>르엔느뷰티</t>
+          <t>네일드메종</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>seolhee10@naver.com</t>
+          <t>doalog13@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1450-9981</t>
+          <t>0507-1375-3528</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>충북 청주시 상당구 상당로143번길 41 1층 르엔느뷰티</t>
+          <t>충북 청주시 흥덕구 서현로 68 상가동 B105호 (뚜레쥬르 옆)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/leannebeauty__</t>
+          <t>https://www.instagram.com/nail_de_maison</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -893,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcfe7o</t>
+          <t>https://talk.naver.com/ct/w5x0t1</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -907,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1540</v>
+        <v>404</v>
       </c>
       <c r="Q5" t="n">
-        <v>67</v>
+        <v>164</v>
       </c>
       <c r="R5" t="n">
-        <v>1607</v>
+        <v>568</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>38426934</t>
+          <t>1226084837</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38426934</t>
+          <t>https://m.place.naver.com/place/1226084837</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -944,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>네일드메종</t>
+          <t>수에브</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>doalog13@naver.com</t>
+          <t>dddd450730@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1375-3528</t>
+          <t>0507-1402-1489</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 서현로 68 상가동 B105호 (뚜레쥬르 옆)</t>
+          <t>충북 청주시 흥덕구 2순환로1219번길 30 힐스에비뉴 청주센트럴 상가2층 234호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_de_maison</t>
+          <t>https://www.instagram.com/_sueve_</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -991,12 +999,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5x0t1</t>
+          <t>https://talk.naver.com/ct/w980geq</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1005,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>404</v>
+        <v>565</v>
       </c>
       <c r="Q6" t="n">
-        <v>164</v>
+        <v>31</v>
       </c>
       <c r="R6" t="n">
-        <v>568</v>
+        <v>596</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1020,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1226084837</t>
+          <t>2071380519</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1226084837</t>
+          <t>https://m.place.naver.com/place/2071380519</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1053,11 @@
           <t>감각네일 용암점</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>dlskgus6327@naver.com</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
@@ -1099,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="Q7" t="n">
         <v>1375</v>
       </c>
       <c r="R7" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1124,7 +1136,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1136,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>복대동 네일코코</t>
+          <t>제이원뷰티</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ejkim0422@naver.com</t>
+          <t>kkkong44@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1371-4016</t>
+          <t>0507-1392-5576</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 증안로34번길 28-13 1층 네일코코</t>
+          <t>충북 청주시 청원구 주성로 293 102호 제이원뷰티</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailcoco_j</t>
+          <t>https://www.instagram.com/j.won_beauty_</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1183,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w443mv</t>
+          <t>https://talk.naver.com/ct/w5wqlj</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1197,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="Q8" t="n">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="R8" t="n">
-        <v>173</v>
+        <v>255</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1212,17 +1224,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1130129691</t>
+          <t>1062324570</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1130129691</t>
+          <t>https://m.place.naver.com/place/1062324570</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1291,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q9" t="n">
         <v>20</v>
       </c>
       <c r="R9" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1316,7 +1328,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1328,29 +1340,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일은봄날</t>
+          <t>복대동 네일코코</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bomnal6878@naver.com</t>
+          <t>appie8003@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1401-6878</t>
+          <t>0507-1371-4016</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 2순환로 1106 서청주파크자이 상가동 120호</t>
+          <t>충북 청주시 흥덕구 증안로34번길 28-13 1층 네일코코</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bomnal_official_</t>
+          <t>https://www.instagram.com/nailcoco_j</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1375,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wek5mvd</t>
+          <t>https://talk.naver.com/ct/w443mv</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1389,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>37</v>
+        <v>165</v>
       </c>
       <c r="Q10" t="n">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="R10" t="n">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1404,17 +1416,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>37892074</t>
+          <t>1130129691</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37892074</t>
+          <t>https://m.place.naver.com/place/1130129691</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1426,29 +1438,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일베이크</t>
+          <t>쏭네일쏭 오창점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ejkim0422@naver.com</t>
+          <t>jsyong25@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1363-0815</t>
+          <t>0507-1353-1373</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충북 청주시 청원구 오창읍 양청택지2길 9 네일베이크</t>
+          <t>충북 청주시 청원구 오창읍 중심상업1로 8-9 1층106호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_bake</t>
+          <t>https://www.instagram.com/ssongnailssong_yb?igsh=MTAzYzRxZWgxaDV2Zg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1473,7 +1485,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4r30v</t>
+          <t>https://talk.naver.com/ct/w8z7nd9</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1487,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>563</v>
+        <v>146</v>
       </c>
       <c r="Q11" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="R11" t="n">
-        <v>604</v>
+        <v>163</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1502,17 +1514,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1210131049</t>
+          <t>2000084923</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1210131049</t>
+          <t>https://m.place.naver.com/place/2000084923</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/청주_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/청주_네일샵.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>프롬네일 청주율량점</t>
+          <t>르엔느뷰티</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jsyong25@naver.com</t>
+          <t>seolhee10@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1336-8451</t>
+          <t>0507-1450-9981</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>충북 청주시 청원구 율량로 152</t>
+          <t>충북 청주시 상당구 상당로143번길 41 1층 르엔느뷰티</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fromnail__</t>
+          <t>http://www.instagram.com/leannebeauty__</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcfe7o</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>930</v>
+        <v>1546</v>
       </c>
       <c r="Q2" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="R2" t="n">
-        <v>991</v>
+        <v>1613</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1014461310</t>
+          <t>38426934</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1014461310</t>
+          <t>https://m.place.naver.com/place/38426934</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>르엔느뷰티</t>
+          <t>프롬네일 청주율량점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>seolhee10@naver.com</t>
+          <t>jsyong25@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1450-9981</t>
+          <t>0507-1336-8451</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>충북 청주시 상당구 상당로143번길 41 1층 르엔느뷰티</t>
+          <t>충북 청주시 청원구 율량로 152</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/leannebeauty__</t>
+          <t>https://www.instagram.com/fromnail__</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -700,14 +704,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcfe7o</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1545</v>
+        <v>930</v>
       </c>
       <c r="Q3" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="R3" t="n">
-        <v>1612</v>
+        <v>991</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>38426934</t>
+          <t>1014461310</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38426934</t>
+          <t>https://m.place.naver.com/place/1014461310</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -820,10 +820,10 @@
         <v>1179</v>
       </c>
       <c r="Q4" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="R4" t="n">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -854,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일드메종</t>
+          <t>벨르뮤 네일&amp;아카데미</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>doalog13@naver.com</t>
+          <t>ye__r2@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1375-3528</t>
+          <t>0507-1456-3478</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 서현로 68 상가동 B105호 (뚜레쥬르 옆)</t>
+          <t>충북 청주시 흥덕구 서현동로 17 4층 403호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_de_maison</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5x0t1</t>
+          <t>https://talk.naver.com/ct/w5y755</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>404</v>
+        <v>785</v>
       </c>
       <c r="Q5" t="n">
-        <v>164</v>
+        <v>362</v>
       </c>
       <c r="R5" t="n">
-        <v>568</v>
+        <v>1147</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1226084837</t>
+          <t>1574225057</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1226084837</t>
+          <t>https://m.place.naver.com/place/1574225057</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1148,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>제이원뷰티</t>
+          <t>엔브뷰티</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kkkong44@naver.com</t>
+          <t>dmsql8424@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1392-5576</t>
+          <t>0507-1331-4116</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충북 청주시 청원구 주성로 293 102호 제이원뷰티</t>
+          <t>충북 청주시 상당구 용담로 7 쁘띠칸타빌 137호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/j.won_beauty_</t>
+          <t>https://http//pf.kakao.com/_Mbxclxb</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1190,17 +1190,13 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5wqlj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1209,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>191</v>
+        <v>153</v>
       </c>
       <c r="Q8" t="n">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="R8" t="n">
-        <v>255</v>
+        <v>173</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1062324570</t>
+          <t>1110185687</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1062324570</t>
+          <t>https://m.place.naver.com/place/1110185687</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1246,29 +1242,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>엔브뷰티</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>dmsql8424@naver.com</t>
-        </is>
-      </c>
+          <t>복대동 네일코코</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1331-4116</t>
+          <t>0507-1371-4016</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충북 청주시 상당구 용담로 7 쁘띠칸타빌 137호</t>
+          <t>충북 청주시 흥덕구 증안로34번길 28-13 1층 네일코코</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://http//pf.kakao.com/_Mbxclxb</t>
+          <t>https://www.instagram.com/nailcoco_j</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1288,13 +1280,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w443mv</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1303,13 +1299,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="R9" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1314,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1110185687</t>
+          <t>1130129691</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1110185687</t>
+          <t>https://m.place.naver.com/place/1130129691</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1340,29 +1336,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>복대동 네일코코</t>
+          <t>쏭네일쏭 오창점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>appie8003@naver.com</t>
+          <t>jsyong25@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1371-4016</t>
+          <t>0507-1353-1373</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 증안로34번길 28-13 1층 네일코코</t>
+          <t>충북 청주시 청원구 오창읍 중심상업1로 8-9 1층106호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailcoco_j</t>
+          <t>https://www.instagram.com/ssongnailssong_yb?igsh=MTAzYzRxZWgxaDV2Zg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1387,7 +1383,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w443mv</t>
+          <t>https://talk.naver.com/ct/w8z7nd9</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="Q10" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="R10" t="n">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,12 +1412,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1130129691</t>
+          <t>2000084923</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1130129691</t>
+          <t>https://m.place.naver.com/place/2000084923</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1438,29 +1434,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>쏭네일쏭 오창점</t>
+          <t>네일뮤토</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jsyong25@naver.com</t>
+          <t>ithgml123@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1353-1373</t>
+          <t>0507-1387-8547</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충북 청주시 청원구 오창읍 중심상업1로 8-9 1층106호</t>
+          <t>충북 청주시 흥덕구 봉명로 188-1 1층 네일뮤토</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ssongnailssong_yb?igsh=MTAzYzRxZWgxaDV2Zg%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/nail_muto_</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1485,12 +1481,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w8z7nd9</t>
+          <t>https://talk.naver.com/ct/w4eny3</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1499,13 +1495,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>146</v>
+        <v>187</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="R11" t="n">
-        <v>163</v>
+        <v>215</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,12 +1510,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2000084923</t>
+          <t>1026077715</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2000084923</t>
+          <t>https://m.place.naver.com/place/1026077715</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
